--- a/data/dividends_info_20261027.xlsx
+++ b/data/dividends_info_20261027.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41.79999923706055</v>
+        <v>43.36000061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2153110087145756</v>
+        <v>0.207564572724</v>
       </c>
       <c r="J2" t="n">
         <v>139</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59.65000152587891</v>
+        <v>60.15000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.173512124213958</v>
+        <v>1.163757243960887</v>
       </c>
       <c r="J3" t="n">
         <v>118</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.640000343322754</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6944444168497026</v>
+        <v>0.6896551875334813</v>
       </c>
       <c r="J4" t="n">
         <v>48</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41.79999923706055</v>
+        <v>43.36000061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2153110087145756</v>
+        <v>0.207564572724</v>
       </c>
       <c r="J6" t="n">
         <v>48</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26.79000091552734</v>
+        <v>26.45499992370605</v>
       </c>
       <c r="I7" t="n">
-        <v>1.717058545277565</v>
+        <v>1.738801743816293</v>
       </c>
       <c r="J7" t="n">
         <v>41</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.065000057220459</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I8" t="n">
-        <v>3.728813455997861</v>
+        <v>3.928571352110661</v>
       </c>
       <c r="J8" t="n">
         <v>27</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51.15000152587891</v>
+        <v>51.70000076293945</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6060605879809371</v>
+        <v>0.5996131439561214</v>
       </c>
       <c r="J9" t="n">
         <v>27</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.79000091552734</v>
+        <v>26.45499992370605</v>
       </c>
       <c r="I10" t="n">
-        <v>1.007838711358571</v>
+        <v>1.020601023544346</v>
       </c>
       <c r="J10" t="n">
         <v>27</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26.63999938964844</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="I11" t="n">
-        <v>2.214714765456254</v>
+        <v>2.198211611944096</v>
       </c>
       <c r="J11" t="n">
         <v>27</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10.23999977111816</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="I12" t="n">
-        <v>2.050781295838534</v>
+        <v>2.027027094201209</v>
       </c>
       <c r="J12" t="n">
         <v>20</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.039999961853027</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>3.311258299058689</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J13" t="n">
         <v>20</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.699999809265137</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I14" t="n">
-        <v>1.228070216532597</v>
+        <v>1.261261217915949</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8.079999923706055</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7425742644373664</v>
+        <v>0.7361963534768861</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10.15999984741211</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>4.527559123115226</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>-1</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7.880000114440918</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4822334955346138</v>
+        <v>0.4922279926520133</v>
       </c>
       <c r="J20" t="n">
         <v>-29</v>
@@ -1799,14 +1799,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1833,14 +1833,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2275,14 +2275,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2615,14 +2615,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3312,14 +3312,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3601,14 +3601,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3676,7 +3676,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3693,7 +3693,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3720,14 +3720,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3771,14 +3771,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3812,7 +3812,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3829,7 +3829,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3863,7 +3863,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3873,14 +3873,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3924,14 +3924,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3992,14 +3992,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4009,14 +4009,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4033,7 +4033,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4094,14 +4094,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4169,7 +4169,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4220,7 +4220,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4264,14 +4264,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4281,14 +4281,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4298,14 +4298,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4315,14 +4315,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4417,14 +4417,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4526,7 +4526,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4628,7 +4628,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4747,7 +4747,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4774,14 +4774,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4832,7 +4832,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4944,14 +4944,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4968,7 +4968,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5029,14 +5029,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5104,7 +5104,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5138,7 +5138,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5189,7 +5189,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5233,14 +5233,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5546,7 +5546,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5607,14 +5607,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5624,14 +5624,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5686,61 +5686,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>